--- a/output/upload/S00026_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
+++ b/output/upload/S00026_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1648,11 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1734,11 +1834,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1820,11 +1940,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1906,11 +2046,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1992,11 +2152,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2078,11 +2258,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2164,11 +2364,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2250,11 +2470,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2336,11 +2576,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2422,11 +2682,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2508,11 +2788,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2594,11 +2894,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2679,8 +2999,31 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2731,8 +3074,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2783,8 +3149,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2835,8 +3224,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2887,8 +3299,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2939,8 +3374,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2991,8 +3449,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3043,8 +3524,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3095,8 +3599,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3147,8 +3674,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3199,8 +3749,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3251,8 +3824,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3303,8 +3899,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3355,8 +3974,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3407,8 +4049,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3459,8 +4124,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3511,8 +4199,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3563,8 +4274,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3615,8 +4349,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3667,8 +4424,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00026_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
+++ b/output/upload/S00026_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">

--- a/output/upload/S00026_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
+++ b/output/upload/S00026_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1339,7 +1339,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>15</v>
       </c>
@@ -1445,7 +1449,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>15</v>
       </c>
@@ -1551,7 +1559,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
         <v>15</v>
       </c>
@@ -1657,7 +1669,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
         <v>15</v>
       </c>
@@ -1763,7 +1779,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J11" s="6" t="n">
         <v>15</v>
       </c>
@@ -1869,7 +1889,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J12" s="6" t="n">
         <v>15</v>
       </c>
@@ -1975,7 +1999,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J13" s="6" t="n">
         <v>15</v>
       </c>
@@ -2081,7 +2109,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="n">
         <v>15</v>
       </c>
@@ -2187,7 +2219,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="n">
         <v>15</v>
       </c>
@@ -2293,7 +2329,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="n">
         <v>15</v>
       </c>
@@ -2399,7 +2439,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="n">
         <v>15</v>
       </c>
@@ -2505,7 +2549,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J18" s="6" t="n">
         <v>15</v>
       </c>
@@ -2611,7 +2659,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J19" s="6" t="n">
         <v>15</v>
       </c>
@@ -2717,7 +2769,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J20" s="6" t="n">
         <v>15</v>
       </c>
@@ -2823,7 +2879,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J21" s="6" t="n">
         <v>15</v>
       </c>
@@ -2929,7 +2989,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J22" s="6" t="n">
         <v>15</v>
       </c>
@@ -3034,6 +3098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J23" t="n">
         <v>15</v>
       </c>
@@ -3109,6 +3178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J24" t="n">
         <v>15</v>
       </c>
@@ -3184,6 +3258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J25" t="n">
         <v>15</v>
       </c>
@@ -3259,6 +3338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J26" t="n">
         <v>15</v>
       </c>
@@ -3334,6 +3418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J27" t="n">
         <v>15</v>
       </c>
@@ -3409,6 +3498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J28" t="n">
         <v>15</v>
       </c>
@@ -3484,6 +3578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J29" t="n">
         <v>15</v>
       </c>
@@ -3559,6 +3658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J30" t="n">
         <v>15</v>
       </c>
@@ -3634,6 +3738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J31" t="n">
         <v>15</v>
       </c>
@@ -3709,6 +3818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J32" t="n">
         <v>15</v>
       </c>
@@ -3784,6 +3898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J33" t="n">
         <v>15</v>
       </c>
@@ -3859,6 +3978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J34" t="n">
         <v>15</v>
       </c>
@@ -3934,6 +4058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J35" t="n">
         <v>15</v>
       </c>
@@ -4009,6 +4138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J36" t="n">
         <v>15</v>
       </c>
@@ -4084,6 +4218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J37" t="n">
         <v>15</v>
       </c>
@@ -4159,6 +4298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J38" t="n">
         <v>15</v>
       </c>
@@ -4234,6 +4378,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J39" t="n">
         <v>15</v>
       </c>
@@ -4309,6 +4458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J40" t="n">
         <v>15</v>
       </c>
@@ -4384,6 +4538,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J41" t="n">
         <v>15</v>
       </c>
@@ -4459,6 +4618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J42" t="n">
         <v>15</v>
       </c>
@@ -4534,6 +4698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J43" t="n">
         <v>15</v>
       </c>
@@ -4609,6 +4778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J44" t="n">
         <v>15</v>
       </c>
@@ -4684,6 +4858,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J45" t="n">
         <v>15</v>
       </c>
@@ -4759,6 +4938,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J46" t="n">
         <v>15</v>
       </c>
@@ -4834,6 +5018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J47" t="n">
         <v>15</v>
       </c>
@@ -4909,6 +5098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J48" t="n">
         <v>15</v>
       </c>
@@ -4984,6 +5178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J49" t="n">
         <v>15</v>
       </c>
@@ -5059,6 +5258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J50" t="n">
         <v>15</v>
       </c>
@@ -5134,6 +5338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J51" t="n">
         <v>15</v>
       </c>
@@ -5209,6 +5418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J52" t="n">
         <v>15</v>
       </c>
@@ -5284,6 +5498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J53" t="n">
         <v>15</v>
       </c>
@@ -5359,6 +5578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J54" t="n">
         <v>15</v>
       </c>
@@ -5434,6 +5658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J55" t="n">
         <v>15</v>
       </c>
@@ -5509,6 +5738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J56" t="n">
         <v>15</v>
       </c>
@@ -5584,6 +5818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J57" t="n">
         <v>15</v>
       </c>
@@ -5659,6 +5898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J58" t="n">
         <v>15</v>
       </c>
@@ -5734,6 +5978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J59" t="n">
         <v>15</v>
       </c>
@@ -5809,6 +6058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J60" t="n">
         <v>15</v>
       </c>
@@ -5884,6 +6138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J61" t="n">
         <v>15</v>
       </c>
@@ -5959,6 +6218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J62" t="n">
         <v>15</v>
       </c>
@@ -6034,6 +6298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J63" t="n">
         <v>15</v>
       </c>
@@ -6109,6 +6378,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J64" t="n">
         <v>15</v>
       </c>
@@ -6184,6 +6458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J65" t="n">
         <v>15</v>
       </c>
@@ -6259,6 +6538,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J66" t="n">
         <v>15</v>
       </c>
@@ -6334,6 +6618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J67" t="n">
         <v>15</v>
       </c>
@@ -6409,6 +6698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J68" t="n">
         <v>15</v>
       </c>
@@ -6484,6 +6778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J69" t="n">
         <v>15</v>
       </c>
@@ -6559,6 +6858,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J70" t="n">
         <v>15</v>
       </c>
@@ -6634,6 +6938,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J71" t="n">
         <v>15</v>
       </c>
@@ -6709,6 +7018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J72" t="n">
         <v>15</v>
       </c>
@@ -6784,6 +7098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J73" t="n">
         <v>15</v>
       </c>
@@ -6859,6 +7178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J74" t="n">
         <v>15</v>
       </c>
@@ -6934,6 +7258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J75" t="n">
         <v>15</v>
       </c>
@@ -7009,6 +7338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J76" t="n">
         <v>15</v>
       </c>
@@ -7084,6 +7418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J77" t="n">
         <v>15</v>
       </c>
@@ -7159,6 +7498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J78" t="n">
         <v>15</v>
       </c>
@@ -7234,6 +7578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J79" t="n">
         <v>15</v>
       </c>
@@ -7309,6 +7658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J80" t="n">
         <v>15</v>
       </c>
@@ -7384,6 +7738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J81" t="n">
         <v>15</v>
       </c>
@@ -7459,6 +7818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J82" t="n">
         <v>15</v>
       </c>
@@ -7534,6 +7898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J83" t="n">
         <v>15</v>
       </c>
@@ -7609,6 +7978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J84" t="n">
         <v>15</v>
       </c>
@@ -7684,6 +8058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J85" t="n">
         <v>15</v>
       </c>
@@ -7759,6 +8138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J86" t="n">
         <v>15</v>
       </c>
@@ -7834,6 +8218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J87" t="n">
         <v>15</v>
       </c>
@@ -7909,6 +8298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J88" t="n">
         <v>15</v>
       </c>
@@ -7984,6 +8378,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J89" t="n">
         <v>15</v>
       </c>
@@ -8059,6 +8458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J90" t="n">
         <v>15</v>
       </c>
@@ -8134,6 +8538,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J91" t="n">
         <v>15</v>
       </c>
@@ -8209,6 +8618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J92" t="n">
         <v>15</v>
       </c>
@@ -8284,6 +8698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J93" t="n">
         <v>15</v>
       </c>
@@ -8359,6 +8778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J94" t="n">
         <v>15</v>
       </c>
@@ -8434,6 +8858,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J95" t="n">
         <v>15</v>
       </c>
@@ -8509,6 +8938,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J96" t="n">
         <v>15</v>
       </c>
@@ -8584,6 +9018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J97" t="n">
         <v>15</v>
       </c>
@@ -8659,6 +9098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J98" t="n">
         <v>15</v>
       </c>
@@ -8734,6 +9178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J99" t="n">
         <v>15</v>
       </c>
@@ -8809,6 +9258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J100" t="n">
         <v>15</v>
       </c>
@@ -8884,6 +9338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J101" t="n">
         <v>15</v>
       </c>
@@ -8959,6 +9418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J102" t="n">
         <v>15</v>
       </c>
@@ -9034,6 +9498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J103" t="n">
         <v>15</v>
       </c>
@@ -9109,6 +9578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J104" t="n">
         <v>15</v>
       </c>
@@ -9184,6 +9658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J105" t="n">
         <v>15</v>
       </c>
@@ -9259,6 +9738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J106" t="n">
         <v>15</v>
       </c>
@@ -9334,6 +9818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J107" t="n">
         <v>15</v>
       </c>
@@ -9409,6 +9898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J108" t="n">
         <v>15</v>
       </c>
@@ -9484,6 +9978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J109" t="n">
         <v>15</v>
       </c>
@@ -9559,6 +10058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J110" t="n">
         <v>15</v>
       </c>
@@ -9634,6 +10138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J111" t="n">
         <v>15</v>
       </c>
@@ -9709,6 +10218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J112" t="n">
         <v>15</v>
       </c>
@@ -9784,6 +10298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J113" t="n">
         <v>15</v>
       </c>
@@ -9859,6 +10378,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J114" t="n">
         <v>15</v>
       </c>
@@ -9934,6 +10458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J115" t="n">
         <v>15</v>
       </c>
@@ -10009,6 +10538,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J116" t="n">
         <v>15</v>
       </c>
@@ -10084,6 +10618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J117" t="n">
         <v>15</v>
       </c>
@@ -10159,6 +10698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J118" t="n">
         <v>15</v>
       </c>
@@ -10234,6 +10778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J119" t="n">
         <v>15</v>
       </c>
@@ -10309,6 +10858,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J120" t="n">
         <v>15</v>
       </c>
@@ -10384,6 +10938,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J121" t="n">
         <v>15</v>
       </c>
@@ -10459,6 +11018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J122" t="n">
         <v>15</v>
       </c>
@@ -10534,6 +11098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J123" t="n">
         <v>15</v>
       </c>
@@ -10609,6 +11178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J124" t="n">
         <v>15</v>
       </c>
@@ -10684,6 +11258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J125" t="n">
         <v>15</v>
       </c>
@@ -10759,6 +11338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J126" t="n">
         <v>15</v>
       </c>
@@ -10834,6 +11418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J127" t="n">
         <v>15</v>
       </c>
@@ -10909,6 +11498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J128" t="n">
         <v>15</v>
       </c>
@@ -10984,6 +11578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J129" t="n">
         <v>15</v>
       </c>
@@ -11059,6 +11658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J130" t="n">
         <v>15</v>
       </c>
@@ -11134,6 +11738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J131" t="n">
         <v>15</v>
       </c>
@@ -11209,6 +11818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J132" t="n">
         <v>15</v>
       </c>
@@ -11284,6 +11898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J133" t="n">
         <v>15</v>
       </c>
@@ -11359,6 +11978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J134" t="n">
         <v>15</v>
       </c>
@@ -11434,6 +12058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J135" t="n">
         <v>15</v>
       </c>
@@ -11509,6 +12138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J136" t="n">
         <v>15</v>
       </c>
@@ -11584,6 +12218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J137" t="n">
         <v>15</v>
       </c>
@@ -11659,6 +12298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J138" t="n">
         <v>15</v>
       </c>
@@ -11734,6 +12378,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J139" t="n">
         <v>15</v>
       </c>
@@ -11809,6 +12458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J140" t="n">
         <v>15</v>
       </c>
@@ -11884,6 +12538,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J141" t="n">
         <v>15</v>
       </c>
@@ -11959,6 +12618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J142" t="n">
         <v>15</v>
       </c>
@@ -12034,6 +12698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J143" t="n">
         <v>15</v>
       </c>
@@ -12109,6 +12778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J144" t="n">
         <v>15</v>
       </c>
@@ -12184,6 +12858,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J145" t="n">
         <v>15</v>
       </c>
@@ -12259,6 +12938,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J146" t="n">
         <v>15</v>
       </c>
@@ -12334,6 +13018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J147" t="n">
         <v>15</v>
       </c>
@@ -12409,6 +13098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J148" t="n">
         <v>15</v>
       </c>
@@ -12484,6 +13178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J149" t="n">
         <v>15</v>
       </c>
@@ -12559,6 +13258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J150" t="n">
         <v>15</v>
       </c>
@@ -12634,6 +13338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J151" t="n">
         <v>15</v>
       </c>
@@ -12709,6 +13418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J152" t="n">
         <v>15</v>
       </c>
@@ -12784,6 +13498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J153" t="n">
         <v>15</v>
       </c>
@@ -12859,6 +13578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J154" t="n">
         <v>15</v>
       </c>
@@ -12934,6 +13658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J155" t="n">
         <v>15</v>
       </c>
@@ -13009,6 +13738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J156" t="n">
         <v>15</v>
       </c>
@@ -13084,6 +13818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J157" t="n">
         <v>15</v>
       </c>
@@ -13159,6 +13898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J158" t="n">
         <v>15</v>
       </c>
@@ -13234,6 +13978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J159" t="n">
         <v>15</v>
       </c>
@@ -13309,6 +14058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J160" t="n">
         <v>15</v>
       </c>
@@ -13384,6 +14138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J161" t="n">
         <v>15</v>
       </c>
@@ -13459,6 +14218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J162" t="n">
         <v>15</v>
       </c>
@@ -13534,6 +14298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J163" t="n">
         <v>15</v>
       </c>
@@ -13609,6 +14378,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J164" t="n">
         <v>15</v>
       </c>
@@ -13684,6 +14458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J165" t="n">
         <v>15</v>
       </c>
@@ -13759,6 +14538,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J166" t="n">
         <v>15</v>
       </c>
@@ -13834,6 +14618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J167" t="n">
         <v>15</v>
       </c>
@@ -13909,6 +14698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J168" t="n">
         <v>15</v>
       </c>
@@ -13984,6 +14778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J169" t="n">
         <v>15</v>
       </c>
@@ -14059,6 +14858,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J170" t="n">
         <v>15</v>
       </c>
@@ -14134,6 +14938,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J171" t="n">
         <v>15</v>
       </c>
@@ -14209,6 +15018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J172" t="n">
         <v>15</v>
       </c>
@@ -14284,6 +15098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J173" t="n">
         <v>15</v>
       </c>
@@ -14359,6 +15178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J174" t="n">
         <v>15</v>
       </c>
@@ -14434,6 +15258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J175" t="n">
         <v>15</v>
       </c>
@@ -14509,6 +15338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J176" t="n">
         <v>15</v>
       </c>
@@ -14584,6 +15418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J177" t="n">
         <v>15</v>
       </c>
@@ -14659,6 +15498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J178" t="n">
         <v>15</v>
       </c>
@@ -14734,6 +15578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J179" t="n">
         <v>15</v>
       </c>
@@ -14809,6 +15658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J180" t="n">
         <v>15</v>
       </c>
@@ -14884,6 +15738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J181" t="n">
         <v>15</v>
       </c>
@@ -14959,6 +15818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J182" t="n">
         <v>15</v>
       </c>
@@ -15034,6 +15898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J183" t="n">
         <v>15</v>
       </c>
@@ -15109,6 +15978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J184" t="n">
         <v>15</v>
       </c>
@@ -15184,6 +16058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J185" t="n">
         <v>15</v>
       </c>
@@ -15259,6 +16138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J186" t="n">
         <v>15</v>
       </c>
@@ -15334,6 +16218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J187" t="n">
         <v>15</v>
       </c>
@@ -15409,6 +16298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J188" t="n">
         <v>15</v>
       </c>
@@ -15484,6 +16378,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J189" t="n">
         <v>15</v>
       </c>
@@ -15559,6 +16458,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J190" t="n">
         <v>15</v>
       </c>
@@ -15634,6 +16538,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J191" t="n">
         <v>15</v>
       </c>
@@ -15709,6 +16618,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J192" t="n">
         <v>15</v>
       </c>
@@ -15784,6 +16698,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J193" t="n">
         <v>15</v>
       </c>
@@ -15859,6 +16778,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J194" t="n">
         <v>15</v>
       </c>
@@ -15934,6 +16858,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J195" t="n">
         <v>15</v>
       </c>
@@ -16009,6 +16938,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J196" t="n">
         <v>15</v>
       </c>
@@ -16084,6 +17018,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J197" t="n">
         <v>15</v>
       </c>
@@ -16159,6 +17098,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J198" t="n">
         <v>15</v>
       </c>
@@ -16234,6 +17178,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J199" t="n">
         <v>15</v>
       </c>
@@ -16309,6 +17258,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J200" t="n">
         <v>15</v>
       </c>
@@ -16384,6 +17338,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J201" t="n">
         <v>15</v>
       </c>
@@ -16459,6 +17418,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J202" t="n">
         <v>15</v>
       </c>
@@ -16534,6 +17498,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J203" t="n">
         <v>15</v>
       </c>
@@ -16609,6 +17578,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J204" t="n">
         <v>15</v>
       </c>
@@ -16684,6 +17658,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J205" t="n">
         <v>15</v>
       </c>
@@ -16759,6 +17738,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J206" t="n">
         <v>15</v>
       </c>
@@ -16834,6 +17818,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J207" t="n">
         <v>15</v>
       </c>
@@ -16909,6 +17898,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J208" t="n">
         <v>15</v>
       </c>
@@ -16984,6 +17978,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J209" t="n">
         <v>15</v>
       </c>
@@ -17059,6 +18058,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J210" t="n">
         <v>15</v>
       </c>
@@ -17134,6 +18138,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J211" t="n">
         <v>15</v>
       </c>
@@ -17209,6 +18218,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J212" t="n">
         <v>15</v>
       </c>
@@ -17284,6 +18298,11 @@
           <t>99991231</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J213" t="n">
         <v>15</v>
       </c>
@@ -17357,6 +18376,11 @@
       <c r="H214" t="inlineStr">
         <is>
           <t>99991231</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="J214" t="n">
